--- a/data/trans_dic/IP31KM06_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 25,64</t>
+          <t>12,68; 30,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,48; 29,65</t>
+          <t>9,87; 27,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,15; 24,44</t>
+          <t>12,84; 25,62</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,14; 29,23</t>
+          <t>27,8; 39,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,85; 39,68</t>
+          <t>20,08; 31,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,12; 33,44</t>
+          <t>25,8; 34,12</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,53; 42,71</t>
+          <t>27,54; 41,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>28,05; 41,14</t>
+          <t>30,45; 43,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,07; 40,25</t>
+          <t>30,86; 39,21</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,46; 61,67</t>
+          <t>40,28; 54,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,16; 54,93</t>
+          <t>35,51; 46,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 55,0</t>
+          <t>39,62; 48,34</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,5%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>30,93; 44,02</t>
+          <t>35,12; 42,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34,22; 42,3</t>
+          <t>30,99; 37,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,28; 41,2</t>
+          <t>34,02; 39,28</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>14871</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4081; 11923</t>
+          <t>4747; 11535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5200; 13427</t>
+          <t>4212; 11648</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11150; 22427</t>
+          <t>10286; 20528</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>59</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>53313</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60749</t>
+          <t>37204</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>98883</t>
+          <t>90518</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28900; 46566</t>
+          <t>43656; 62678</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50671; 72208</t>
+          <t>29214; 45893</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85733; 114115</t>
+          <t>78048; 103234</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>82</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62579</t>
+          <t>67633</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>63318</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135681</t>
+          <t>130952</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>51113; 73922</t>
+          <t>55122; 82059</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59611; 87419</t>
+          <t>53180; 75336</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>119776; 155198</t>
+          <t>115666; 146949</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>136</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>122071</t>
+          <t>136557</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>141733</t>
+          <t>103487</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263804</t>
+          <t>240044</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>99995; 169148</t>
+          <t>117706; 157816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>122487; 167543</t>
+          <t>90658; 117806</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>233685; 318621</t>
+          <t>216956; 264698</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>290</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>230130</t>
+          <t>265182</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>284334</t>
+          <t>211202</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>514464</t>
+          <t>476384</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>202004; 287541</t>
+          <t>241225; 291196</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>254866; 315021</t>
+          <t>191598; 234513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>479166; 575961</t>
+          <t>444019; 512656</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM06_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>20,51%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>12,68; 30,81</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9,87; 27,29</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12,84; 25,62</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>29,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>27,8; 39,91</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20,08; 31,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25,8; 34,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>33,8%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,54; 41,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30,45; 43,13</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>30,86; 39,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>46,73%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>40,53%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>43,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>40,28; 54,01</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>35,51; 46,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>39,62; 48,34</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>38,61%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36,5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>35,12; 42,4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30,99; 37,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34,02; 39,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.2051054706514406</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1685260561593367</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1856182403903208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7678</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7193</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14871</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1267985718005237</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.09867998842984778</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.128389777307397</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4747; 11535</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4212; 11648</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10286; 20528</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.3081314903676272</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.2729129163921838</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.2562271905264931</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.3394835439174651</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.2556693690499958</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.2991726805857065</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>53313</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37204</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90518</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.2779892639215935</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.2007557400998847</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.2579574672420643</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>43656; 62678</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>29214; 45893</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>78048; 103234</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.3991193238734025</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.315379744676024</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.341202202406939</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.3379543971027842</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3624971784942623</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3493924045395052</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>67633</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>63318</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130952</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.2754340016437548</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.3044569629694983</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.3086091137319799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>55122; 82059</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>53180; 75336</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>115666; 146949</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.4100352967849256</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.4312983262827457</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3920739079888415</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4673085998198229</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.4052949590444558</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.4383904088191436</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>136557</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>103487</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>240044</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.4027994297650179</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.3550513186559536</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.3962246708293252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>117706; 157816</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>90658; 117806</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>216956; 264698</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.5400572944459845</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.4613743646497528</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.4834146372143814</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.3860990997494866</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3416364053299036</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.3650366333780123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>265182</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>211202</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>476384</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3512185179999625</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.3099249400451485</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.3402364075073516</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>241225; 291196</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>191598; 234513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>444019; 512656</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.4239741178621034</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3793427307052015</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.392830887834407</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que acuden una vez o más a la semana a un centro de comida rápida (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>7678</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>7193</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>14871</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4747</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4212</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>10286</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>11535</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>11648</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>20528</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>53313</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>37204</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>90518</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>43656</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>29214</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>78048</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>62678</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>45893</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>103234</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>82</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>67633</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>63318</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>130952</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>55122</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>53180</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>115666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>82059</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>75336</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>146949</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>136</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>136557</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>103487</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>240044</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>117706</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>90658</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>216956</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>157816</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>117806</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>264698</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>332</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>290</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>265182</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>211202</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>476384</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>241225</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>191598</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>444019</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>291196</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>234513</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>512656</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>